--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-15.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-15.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583998917888</v>
+        <v>5583996181993</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vamberto</t>
+          <t>Lucia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vamberto Almeida Cardoso</t>
+          <t>Lucia Medeiros</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583996481861</v>
+        <v>5583998114186</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Rayan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Residencial e Empresarial Julio Faustino Monteiro</t>
+          <t>Rayan Honorio da Silva</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583981297171</v>
+        <v>5583981597656</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>Thiberio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paulo Sergio da Silva</t>
+          <t>Thiberio Rickelly Pereira de Matos</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5511964564696</v>
+        <v>5583996942142</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alcemir</t>
+          <t>Elcio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alcemir Braz de Macedo</t>
+          <t>Elcio Dias Meira</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583994183390</v>
+        <v>5583988502451</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sidney</t>
+          <t>Americo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sidney Silva</t>
+          <t>Americo da Silva</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583998225417</v>
+        <v>5583986345900</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Antony</t>
+          <t>Amaralina</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Antony Mateus Lima de Jesus</t>
+          <t>Amaralina de Assis Meireles</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583996290822</v>
+        <v>5583998948060</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ricardo</t>
+          <t>Giovanna</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ricardo Pequeno da Silva</t>
+          <t>Giovanna Karen Silva de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583988457712</v>
+        <v>5583999220728</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Leidiane</t>
+          <t>Robson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Leidiane do Livramento Bezerra</t>
+          <t>Robson Fernandes da Silva</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583991514259</v>
+        <v>5583998917888</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Osvaldo</t>
+          <t>Vamberto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Osvaldo Santos da Costa</t>
+          <t>Vamberto Almeida Cardoso</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583999167537</v>
+        <v>5583996481861</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Agamenon</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Agamenon da Silva Costa</t>
+          <t>Residencial e Empresarial Julio Faustino Monteiro</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583987505411</v>
+        <v>5583981297171</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Severino</t>
+          <t>Paulo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Severino de Medeiros Marques</t>
+          <t>Paulo Sergio da Silva</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583987851255</v>
+        <v>5511964564696</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rozenilda</t>
+          <t>Alcemir</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rozenilda Menezes Mota Meira</t>
+          <t>Alcemir Braz de Macedo</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583988650542</v>
+        <v>5583993397750</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Gean</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Leandro Carneiro da Silva</t>
+          <t>Gean de Jesus Figueira</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583988161857</v>
+        <v>5583994183390</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Solange</t>
+          <t>Sidney</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Solange Maria Eloi do Monte</t>
+          <t>Sidney Silva</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583987702417</v>
+        <v>5583998225417</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Inaldo</t>
+          <t>Antony</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Inaldo de Oliveira Matias</t>
+          <t>Antony Mateus Lima de Jesus</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583999632321</v>
+        <v>5583996290822</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Obrux</t>
+          <t>Ricardo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Obrux Omnia Resistit Studere</t>
+          <t>Ricardo Pequeno da Silva</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583999288121</v>
+        <v>5583988457712</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Marcio</t>
+          <t>Leidiane</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Marcio da Silva Marcone</t>
+          <t>Leidiane do Livramento Bezerra</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583987243798</v>
+        <v>5583991514259</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Osvaldo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alex Lins Bezerra</t>
+          <t>Osvaldo Santos da Costa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583987727083</v>
+        <v>5583999167537</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Edson</t>
+          <t>Agamenon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Edson Barros</t>
+          <t>Agamenon da Silva Costa</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583996822433</v>
+        <v>5583987505411</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Severino</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jose Canuto dos Santos Filho</t>
+          <t>Severino de Medeiros Marques</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583999260041</v>
+        <v>5583987851255</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Rozenilda</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ana Cristina Mendonça Marinho do Rego</t>
+          <t>Rozenilda Menezes Mota Meira</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583988074783</v>
+        <v>5583988650542</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Heber</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Heber Newton da Silva Elias</t>
+          <t>Leandro Carneiro da Silva</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583993022626</v>
+        <v>5583988161857</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rosana</t>
+          <t>Solange</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rosana Maria dos Santos</t>
+          <t>Solange Maria Eloi do Monte</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583993227895</v>
+        <v>5583987702417</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alexsander</t>
+          <t>Inaldo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alexsander Farias de Oliveira</t>
+          <t>Inaldo de Oliveira Matias</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583988158555</v>
+        <v>5583999632321</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Glaydes</t>
+          <t>Obrux</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Glaydes Maria Lyra Lins</t>
+          <t>Obrux Omnia Resistit Studere</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583987000957</v>
+        <v>5583999288121</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Francisca</t>
+          <t>Marcio</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Francisca Nayara Nunes de Araujo</t>
+          <t>Marcio da Silva Marcone</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5531988048963</v>
+        <v>5583987243798</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pollyanna</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pollyanna Cristina Martins da Silva</t>
+          <t>Alex Lins Bezerra</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583989112601</v>
+        <v>5583987727083</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Valdemir</t>
+          <t>Edson</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Valdemir Vitorino de Melo</t>
+          <t>Edson Barros</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583988019605</v>
+        <v>5583996822433</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fabiano</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fabiano Araujo</t>
+          <t>Jose Canuto dos Santos Filho</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583987346532</v>
+        <v>5583999260041</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Joselito</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Joselito dos Santos Santana</t>
+          <t>Ana Cristina Mendonça Marinho do Rego</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583988200363</v>
+        <v>5583988074783</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Heber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jose Ferreira Lima</t>
+          <t>Heber Newton da Silva Elias</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583987818216</v>
+        <v>5583993022626</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Josenildo</t>
+          <t>Rosana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Josenildo Damiao dos Santos</t>
+          <t>Rosana Maria dos Santos</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583987506099</v>
+        <v>5583993227895</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jonata</t>
+          <t>Alexsander</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jonata Firmino</t>
+          <t>Alexsander Farias de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583987178381</v>
+        <v>5583988158555</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Josenilda</t>
+          <t>Glaydes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Josenilda Maria da Silva Elias</t>
+          <t>Glaydes Maria Lyra Lins</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583999306150</v>
+        <v>5583987000957</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Francisca</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Joao Eudes Gomes</t>
+          <t>Francisca Nayara Nunes de Araujo</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583981091728</v>
+        <v>5531988048963</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Valdenira</t>
+          <t>Pollyanna</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valdenira da Silva Leite</t>
+          <t>Pollyanna Cristina Martins da Silva</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583996741242</v>
+        <v>5583989112601</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Valdemir</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Maria Jose da Silva Pereira</t>
+          <t>Valdemir Vitorino de Melo</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583991874176</v>
+        <v>5583988019605</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Matheus</t>
+          <t>Fabiano</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Matheus Antonius Porciuncula Pereira</t>
+          <t>Fabiano Araujo</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583991337474</v>
+        <v>5583987346532</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Joselito</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jose Francisco Silva Oliveira</t>
+          <t>Joselito dos Santos Santana</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583986334752</v>
+        <v>5583988200363</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mayara</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mayara Kelly Machado de Oliveira Garcia</t>
+          <t>Jose Ferreira Lima</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583999457342</v>
+        <v>5583987818216</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Josenildo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Joao Victor Pereira</t>
+          <t>Josenildo Damiao dos Santos</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583987251935</v>
+        <v>5583987506099</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mercia</t>
+          <t>Jonata</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mercia Rodrigues</t>
+          <t>Jonata Firmino</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583999743652</v>
+        <v>5583987178381</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Arthur</t>
+          <t>Josenilda</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Arthur Vinicios</t>
+          <t>Josenilda Maria da Silva Elias</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5581998510204</v>
+        <v>5583999306150</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Andre Tavares</t>
+          <t>Joao Eudes Gomes</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583999196276</v>
+        <v>5583981091728</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Weslley</t>
+          <t>Valdenira</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Weslley Lucas</t>
+          <t>Valdenira da Silva Leite</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583991115796</v>
+        <v>5583996741242</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Natanael</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Natanael Pereira Duda</t>
+          <t>Maria Jose da Silva Pereira</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583993937878</v>
+        <v>5583991874176</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ivanildo</t>
+          <t>Matheus</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ivanildo Gomes Ramos</t>
+          <t>Matheus Antonius Porciuncula Pereira</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583988985748</v>
+        <v>5583991337474</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Madalena</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Madalena da Silva Souza</t>
+          <t>Jose Francisco Silva Oliveira</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583996030595</v>
+        <v>5583986334752</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Clesio</t>
+          <t>Mayara</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Clesio Luis Leite</t>
+          <t>Mayara Kelly Machado de Oliveira Garcia</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5521982299342</v>
+        <v>5583999457342</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ariberto</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ariberto Mendonça Falcao</t>
+          <t>Joao Victor Pereira</t>
         </is>
       </c>
     </row>
